--- a/docs/Example Files/CRYSS V2.0 Input File Templates/5 Component Mixture.xlsx
+++ b/docs/Example Files/CRYSS V2.0 Input File Templates/5 Component Mixture.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\06 website\idiocratease-iggy.github.io\docs\Example Files\CRYSS V2.0 Input File Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17340EC3-7998-40C8-9897-1EC5ECABF198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A422571-7E16-450F-B9CD-20657FCDB30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="40140" windowHeight="15030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="0" windowWidth="31980" windowHeight="16116" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="slice_records" sheetId="1" r:id="rId1"/>
+    <sheet name="CRYSS Input File V2.0" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -247,24 +247,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -272,12 +278,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -583,47 +583,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="22" width="12.5703125" customWidth="1"/>
+    <col min="18" max="22" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="12"/>
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="8"/>
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="11" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="8" t="s">
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="14" t="s">
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="16"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="18"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -671,26 +671,26 @@
       <c r="P2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="Q2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="R2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="S2" s="18" t="s">
+      <c r="S2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="18" t="s">
+      <c r="T2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="U2" s="18" t="s">
+      <c r="U2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="V2" s="18" t="s">
+      <c r="V2" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -712,7 +712,7 @@
       <c r="T3" s="6"/>
       <c r="V3" s="7"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -734,7 +734,7 @@
       <c r="T4" s="6"/>
       <c r="V4" s="7"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -756,7 +756,7 @@
       <c r="T5" s="6"/>
       <c r="V5" s="7"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -778,7 +778,7 @@
       <c r="T6" s="6"/>
       <c r="V6" s="7"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -800,7 +800,7 @@
       <c r="T7" s="6"/>
       <c r="V7" s="7"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -822,7 +822,7 @@
       <c r="T8" s="6"/>
       <c r="V8" s="7"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -844,7 +844,7 @@
       <c r="T9" s="6"/>
       <c r="V9" s="7"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -866,7 +866,7 @@
       <c r="T10" s="6"/>
       <c r="V10" s="7"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -888,7 +888,7 @@
       <c r="T11" s="6"/>
       <c r="V11" s="7"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -910,7 +910,7 @@
       <c r="T12" s="6"/>
       <c r="V12" s="7"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -932,7 +932,7 @@
       <c r="T13" s="6"/>
       <c r="V13" s="7"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -954,70 +954,70 @@
       <c r="T14" s="6"/>
       <c r="V14" s="7"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="Q15" s="5"/>
       <c r="R15" s="6"/>
       <c r="S15" s="5"/>
       <c r="T15" s="6"/>
       <c r="V15" s="7"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="Q16" s="5"/>
       <c r="R16" s="6"/>
       <c r="S16" s="5"/>
       <c r="T16" s="6"/>
       <c r="V16" s="7"/>
     </row>
-    <row r="17" spans="17:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="17:22" x14ac:dyDescent="0.3">
       <c r="Q17" s="5"/>
       <c r="R17" s="6"/>
       <c r="S17" s="5"/>
       <c r="T17" s="6"/>
       <c r="V17" s="7"/>
     </row>
-    <row r="18" spans="17:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="17:22" x14ac:dyDescent="0.3">
       <c r="Q18" s="5"/>
       <c r="R18" s="6"/>
       <c r="S18" s="5"/>
       <c r="T18" s="6"/>
       <c r="V18" s="7"/>
     </row>
-    <row r="19" spans="17:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="17:22" x14ac:dyDescent="0.3">
       <c r="Q19" s="5"/>
       <c r="R19" s="6"/>
       <c r="S19" s="5"/>
       <c r="T19" s="6"/>
       <c r="V19" s="7"/>
     </row>
-    <row r="20" spans="17:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="17:22" x14ac:dyDescent="0.3">
       <c r="Q20" s="5"/>
       <c r="R20" s="6"/>
       <c r="S20" s="5"/>
       <c r="T20" s="6"/>
       <c r="V20" s="7"/>
     </row>
-    <row r="21" spans="17:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="17:22" x14ac:dyDescent="0.3">
       <c r="Q21" s="5"/>
       <c r="R21" s="6"/>
       <c r="S21" s="5"/>
       <c r="T21" s="6"/>
       <c r="V21" s="7"/>
     </row>
-    <row r="22" spans="17:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="17:22" x14ac:dyDescent="0.3">
       <c r="Q22" s="5"/>
       <c r="R22" s="6"/>
       <c r="S22" s="5"/>
       <c r="T22" s="6"/>
       <c r="V22" s="7"/>
     </row>
-    <row r="23" spans="17:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="17:22" x14ac:dyDescent="0.3">
       <c r="Q23" s="5"/>
       <c r="R23" s="6"/>
       <c r="S23" s="5"/>
       <c r="T23" s="6"/>
       <c r="V23" s="7"/>
     </row>
-    <row r="24" spans="17:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="17:22" x14ac:dyDescent="0.3">
       <c r="Q24" s="5"/>
       <c r="R24" s="6"/>
       <c r="S24" s="5"/>
